--- a/11_FINAL_PROJECT_&_PORTOFOLIO/Selasa 8 September/04_Data_Cleaning_Log.xlsx
+++ b/11_FINAL_PROJECT_&_PORTOFOLIO/Selasa 8 September/04_Data_Cleaning_Log.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Data Cleaning Log - Sales Performance Analysis (Superstore Dataset)</t>
+          <t>Data Cleaning Log - Customer Behavior Analysis (Superstore Dataset)</t>
         </is>
       </c>
     </row>
